--- a/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240223120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
@@ -83,7 +83,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
@@ -7,9 +7,9 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_A05_TypeDocC" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE-A04-Loinc" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_A12_Nomencla" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>

--- a/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J66-TypeCode-DMP.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="251">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240223120000</t>
+    <t>20240927120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -368,6 +368,12 @@
     <t>Plan personnalisé de soins</t>
   </si>
   <si>
+    <t>28617-9</t>
+  </si>
+  <si>
+    <t>Bilan bucco-dentaire</t>
+  </si>
+  <si>
     <t>28653-4</t>
   </si>
   <si>
@@ -386,6 +392,12 @@
     <t>CR hospitalier (séjour)</t>
   </si>
   <si>
+    <t>34120-6</t>
+  </si>
+  <si>
+    <t>Bilan par professionnel de santé</t>
+  </si>
+  <si>
     <t>34133-9</t>
   </si>
   <si>
@@ -425,7 +437,7 @@
     <t>47420-5</t>
   </si>
   <si>
-    <t>CR de bilan fonctionnel (par auxiliaire médical)</t>
+    <t>CR de bilan fonctionnel</t>
   </si>
   <si>
     <t>52040-3</t>
@@ -500,6 +512,12 @@
     <t>Attestation de consentement</t>
   </si>
   <si>
+    <t>60280-5</t>
+  </si>
+  <si>
+    <t>Fiche de retour du service des urgences</t>
+  </si>
+  <si>
     <t>60568-3</t>
   </si>
   <si>
@@ -509,7 +527,7 @@
     <t>60591-5</t>
   </si>
   <si>
-    <t>Synthèse du dossier médical</t>
+    <t>Synthèse médicale</t>
   </si>
   <si>
     <t>60593-1</t>
@@ -551,7 +569,7 @@
     <t>74207-2</t>
   </si>
   <si>
-    <t>Dossier de liaison d'urgence</t>
+    <t>Document de liaison d'urgence</t>
   </si>
   <si>
     <t>74465-6</t>
@@ -596,6 +614,12 @@
     <t>Planification thérapeutique</t>
   </si>
   <si>
+    <t>78341-5</t>
+  </si>
+  <si>
+    <t>Fiche de transfert vers le service des urgences</t>
+  </si>
+  <si>
     <t>78489-2</t>
   </si>
   <si>
@@ -686,6 +710,12 @@
     <t>Lettre de liaison d'entrée en structure sociale ou médico-sociale</t>
   </si>
   <si>
+    <t>89233-1</t>
+  </si>
+  <si>
+    <t>CR de grossesse</t>
+  </si>
+  <si>
     <t>89235-6</t>
   </si>
   <si>
@@ -713,7 +743,7 @@
     <t>96173-0</t>
   </si>
   <si>
-    <t>Attestation de dépistage</t>
+    <t>Test rapide d'orientation diagnostique</t>
   </si>
   <si>
     <t>96874-3</t>
@@ -722,7 +752,13 @@
     <t>COVID-19 Attestation de vaccination</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A04-Loinc/FHIR/TRE-A04-Loinc</t>
+    <t>101881-1</t>
+  </si>
+  <si>
+    <t>Carte d'implant</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>E1762</t>
@@ -1287,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1864,18 +1900,66 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>92</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="B73" t="s" s="2">
-        <v>235</v>
+      <c r="B79" t="s" s="2">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -1902,10 +1986,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
@@ -1921,7 +2005,7 @@
         <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
